--- a/data/trans_orig/P25C_R2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3725</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43250</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104190</t>
+          <t>105693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167452</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175364</t>
+          <t>175367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63118</t>
+          <t>63223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42278</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48250</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108814</t>
+          <t>109109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116339</t>
+          <t>116435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148524</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152224</t>
+          <t>152209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44922</t>
+          <t>44929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>55972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113247</t>
+          <t>113848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121058</t>
+          <t>121059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>84671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92612</t>
+          <t>92421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201441</t>
+          <t>202042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212071</t>
+          <t>212232</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323240</t>
+          <t>323785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>345806</t>
+          <t>345664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>32110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37429</t>
+          <t>37410</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359331</t>
+          <t>359209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382785</t>
+          <t>383203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39568</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>825428</t>
+          <t>825958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>844555</t>
+          <t>844082</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>317645</t>
+          <t>318278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329169</t>
+          <t>329494</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1147610</t>
+          <t>1147428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1173904</t>
+          <t>1173753</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R2_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>49680</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58831</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>117602</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105693</t>
+          <t>113442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64213</t>
+          <t>65470</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>62650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>173698</t>
+          <t>183072</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168585</t>
+          <t>178600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175367</t>
+          <t>184739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>118605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>185348</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>66762</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63223</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45974</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>113723</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109109</t>
+          <t>108565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116435</t>
+          <t>115564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>106844</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90895</t>
+          <t>104246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57275</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>61581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>151166</t>
+          <t>170943</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148408</t>
+          <t>168335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152209</t>
+          <t>172048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>39922</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44929</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>54173</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>55536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>118491</t>
+          <t>138583</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113848</t>
+          <t>133549</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>141515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>95857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>104633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>208253</t>
+          <t>240116</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>202042</t>
+          <t>233943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212232</t>
+          <t>244423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121824</t>
+          <t>142359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>107408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>216648</t>
+          <t>249767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>340682</t>
+          <t>107449</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323785</t>
+          <t>101422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>345664</t>
+          <t>110705</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>41451</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32110</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37410</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>376241</t>
+          <t>148900</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359209</t>
+          <t>142763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383203</t>
+          <t>152731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>113542</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>157783</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>21661</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>835390</t>
+          <t>645289</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>825958</t>
+          <t>636746</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>844082</t>
+          <t>650992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>324220</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318278</t>
+          <t>344510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329494</t>
+          <t>356698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1159610</t>
+          <t>996648</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1147428</t>
+          <t>985985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1173753</t>
+          <t>1004448</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
